--- a/door_switch_maze/grid/DDQN_HER_mission/episode_rewards_ddqn_her.xlsx
+++ b/door_switch_maze/grid/DDQN_HER_mission/episode_rewards_ddqn_her.xlsx
@@ -469,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.45296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.4768749999999999</v>
       </c>
     </row>
     <row r="21">
@@ -781,7 +781,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.62453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -861,7 +861,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>0.8903125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -917,7 +917,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>0.46421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -965,7 +965,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.6765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1013,7 +1013,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>0.4796874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1021,7 +1021,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>0.83125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1045,7 +1045,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5584375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1061,7 +1061,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.375625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1069,7 +1069,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.4093749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1077,7 +1077,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3221875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.59078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1141,7 +1141,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.56265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1157,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0.38125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1173,7 +1173,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.67234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.6343749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1237,7 +1237,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.5696874999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1245,7 +1245,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>0.87484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1277,7 +1277,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>0.35734375</v>
+        <v>0.53171875</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>0.45859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1341,7 +1341,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>0.62734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -1349,7 +1349,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>0.6653125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -1357,7 +1357,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>0.4571875</v>
+        <v>0.41921875</v>
       </c>
     </row>
     <row r="117">
@@ -1365,7 +1365,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9184375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1373,7 +1373,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>0.39390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1389,7 +1389,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>0.75109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1397,7 +1397,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>0.94515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.3671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1429,7 +1429,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>0.63015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -1445,7 +1445,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>0.6793750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -1469,7 +1469,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>0.769375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1485,7 +1485,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>0.8579687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -1501,7 +1501,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>0.88046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1541,7 +1541,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0.6850000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1549,7 +1549,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>0.83828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -1557,7 +1557,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0.5021875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -1573,7 +1573,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0.46421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.6498437500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1605,7 +1605,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>0.87484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -1621,7 +1621,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0.68921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -1637,7 +1637,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.9282812499999999</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.32359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -1677,7 +1677,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0.803125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -1693,7 +1693,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>0.85375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -1701,7 +1701,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>0.69765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -1709,7 +1709,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.4178125</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>0.55984375</v>
+        <v>0.6399999999999999</v>
       </c>
     </row>
     <row r="162">
@@ -1733,7 +1733,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.6174999999999999</v>
       </c>
     </row>
     <row r="164">
@@ -1741,7 +1741,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0.6625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -1757,7 +1757,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>0.656875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -1773,7 +1773,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.80875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -1797,7 +1797,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>0.81859375</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="172">
@@ -1805,7 +1805,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>0.52046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -1821,7 +1821,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.7581249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -1837,7 +1837,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>0.3165625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -1845,7 +1845,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>0.8256250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -1869,7 +1869,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>0.7103124999999999</v>
       </c>
     </row>
     <row r="181">
@@ -1909,7 +1909,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>0.3151562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -1917,7 +1917,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>0.60765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -1925,7 +1925,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>0.7876562499999999</v>
       </c>
     </row>
     <row r="188">
@@ -1949,7 +1949,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>0.83828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -1957,7 +1957,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>0.6751562499999999</v>
+        <v>0.62453125</v>
       </c>
     </row>
     <row r="192">
@@ -1973,7 +1973,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>0.4037500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -1981,7 +1981,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>0.66390625</v>
       </c>
     </row>
     <row r="195">
@@ -1997,7 +1997,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>0.5021875</v>
       </c>
     </row>
     <row r="197">
@@ -2029,7 +2029,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>0.4417187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -2037,7 +2037,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>0.32078125</v>
+        <v>0.4628125</v>
       </c>
     </row>
     <row r="202">
@@ -2045,7 +2045,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>0.7215625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>0.75953125</v>
+        <v>0.5049999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -2069,7 +2069,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>0.89453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -2077,7 +2077,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>0.35453125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -2085,7 +2085,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>0.5978125</v>
+        <v>0.35734375</v>
       </c>
     </row>
     <row r="208">
@@ -2101,7 +2101,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0.34609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -2109,7 +2109,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>0.80734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -2117,7 +2117,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>0.4009374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -2133,7 +2133,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>0.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2149,7 +2149,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>0.4740625000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -2165,7 +2165,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0.92125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -2173,7 +2173,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>0.8425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -2181,7 +2181,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>0.9128125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -2189,7 +2189,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>0.7890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -2213,7 +2213,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>0.8396875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -2221,7 +2221,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>0.5921875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -2229,7 +2229,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>0.6582812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -2237,7 +2237,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0.9325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -2245,7 +2245,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>0.33765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -2261,7 +2261,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0.8340624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -2285,7 +2285,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>0.5106250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0.84390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>0.870625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -2309,7 +2309,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0.44875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.4557812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -2325,7 +2325,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0.5725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -2341,7 +2341,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>0.533125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -2357,7 +2357,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0.60203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -2373,7 +2373,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="244">
@@ -2381,7 +2381,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>0.938125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -2405,7 +2405,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0.4445312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0.75671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.90859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -2437,7 +2437,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>0.7637499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -2445,7 +2445,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>0.5289062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -2461,7 +2461,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0.9521875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -2469,7 +2469,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>0.9521875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -2477,7 +2477,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>0.93671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -2501,7 +2501,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>0.9662500000000001</v>
+        <v>0.5190625</v>
       </c>
     </row>
     <row r="260">
@@ -2557,7 +2557,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>0.9339062499999999</v>
       </c>
     </row>
     <row r="267">
@@ -2565,7 +2565,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>0.68078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -2573,7 +2573,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>0.89171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -2581,7 +2581,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>0.56125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -2597,7 +2597,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>0.47546875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -2605,7 +2605,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>0.7792187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -2621,7 +2621,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>0.9634374999999999</v>
+        <v>0.443125</v>
       </c>
     </row>
     <row r="275">
@@ -2629,7 +2629,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>0.7834375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -2653,7 +2653,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>0.4628125</v>
       </c>
     </row>
     <row r="279">
@@ -2677,7 +2677,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>0.9339062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -2685,7 +2685,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0.66109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -2717,7 +2717,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0.59078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -2725,7 +2725,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>0.3095312499999999</v>
       </c>
     </row>
     <row r="288">
@@ -2733,7 +2733,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -2749,7 +2749,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>0.94375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -2765,7 +2765,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>0.55421875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -2773,7 +2773,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>0.9775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -2781,7 +2781,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>0.971875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -2789,7 +2789,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>0.96484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -2797,7 +2797,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>0.94515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -2813,7 +2813,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.5879687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -2829,7 +2829,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>0.94796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0.9240625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>0.7159375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -2869,7 +2869,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>0.915625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -2877,7 +2877,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>0.836875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -2885,7 +2885,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>0.8495312500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -2909,7 +2909,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0.566875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>0.86640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -2925,7 +2925,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>0.8635937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -2949,7 +2949,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0.61328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>0.3953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -2989,7 +2989,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9310937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -3005,7 +3005,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -3021,7 +3021,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>0.904375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.73140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -3037,7 +3037,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>0.7792187500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -3045,7 +3045,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>0.9015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -3061,7 +3061,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>0.97328125</v>
+        <v>0.6821874999999999</v>
       </c>
     </row>
     <row r="330">
@@ -3085,7 +3085,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="n">
-        <v>0.6765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -3093,7 +3093,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>0.9071875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -3101,7 +3101,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>0.94515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -3133,7 +3133,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>0.88046875</v>
+        <v>0.60765625</v>
       </c>
     </row>
     <row r="339">
@@ -3149,7 +3149,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>0.8256250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -3165,7 +3165,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>0.87765625</v>
+        <v>0.3306249999999999</v>
       </c>
     </row>
     <row r="343">
@@ -3173,7 +3173,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -3181,7 +3181,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>0.97328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -3189,7 +3189,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="n">
-        <v>0.465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -3197,7 +3197,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>0.3559375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -3205,7 +3205,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>0.82984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>0.8256250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>0.48953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>0.31375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -3237,7 +3237,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>0.94796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -3245,7 +3245,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>0.836875</v>
+        <v>0.70609375</v>
       </c>
     </row>
     <row r="353">
@@ -3285,7 +3285,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="n">
-        <v>0.87203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -3293,7 +3293,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>0.88046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -3301,7 +3301,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>0.91140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>0.3995312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -3325,7 +3325,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>0.74828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -3341,7 +3341,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>0.53171875</v>
+        <v>0.41921875</v>
       </c>
     </row>
     <row r="365">
@@ -3349,7 +3349,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>0.9325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -3357,7 +3357,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>0.5035937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -3381,7 +3381,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>0.74125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -3405,7 +3405,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>0.6695312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>0.7904687500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>0</v>
+        <v>0.5289062499999999</v>
       </c>
     </row>
     <row r="375">
@@ -3429,7 +3429,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>0.9296875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -3445,7 +3445,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>0.89734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -3453,7 +3453,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="n">
-        <v>0.70046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -3469,7 +3469,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>0.949375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -3477,7 +3477,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>0.81015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -3485,7 +3485,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>0.8959375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -3501,7 +3501,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>0.5401562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>0.48390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -3517,7 +3517,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>0.6048437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -3525,7 +3525,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>0.58515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -3533,7 +3533,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>0.3728125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0.8931249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -3549,7 +3549,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>0.62171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -3557,7 +3557,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>0.90296875</v>
+        <v>0.2996875</v>
       </c>
     </row>
     <row r="392">
@@ -3573,7 +3573,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>0.7609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="n">
-        <v>0.94375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -3589,7 +3589,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>0.90578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -3613,7 +3613,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0.78203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -3621,7 +3621,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="n">
-        <v>0.9662500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="n">
-        <v>0.8635937499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -3637,7 +3637,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="n">
-        <v>0.84109375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -3645,7 +3645,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="n">
-        <v>0.64140625</v>
+        <v>0.3728125</v>
       </c>
     </row>
     <row r="403">
@@ -3653,7 +3653,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="n">
-        <v>0.904375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -3661,7 +3661,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>0.85234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -3669,7 +3669,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0.735625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -3677,7 +3677,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0.7665625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -3685,7 +3685,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="n">
-        <v>0.9339062499999999</v>
+        <v>0.6540625</v>
       </c>
     </row>
     <row r="408">
@@ -3701,7 +3701,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>0.915625</v>
+        <v>0.8003125</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>0.7946875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="n">
-        <v>0.7173437499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -3725,7 +3725,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>0.3292187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -3733,7 +3733,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="n">
-        <v>0.9282812499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -3765,7 +3765,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="n">
-        <v>0.3995312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -3781,7 +3781,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="n">
-        <v>0.865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -3789,7 +3789,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="n">
-        <v>0.94796875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -3797,7 +3797,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="n">
-        <v>0.75390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422">
@@ -3805,7 +3805,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.5303125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -3813,7 +3813,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="n">
-        <v>0.47828125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -3853,7 +3853,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="n">
-        <v>0.8579687499999999</v>
+        <v>0.6174999999999999</v>
       </c>
     </row>
     <row r="429">
@@ -3885,7 +3885,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="n">
-        <v>0.6596875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -3893,7 +3893,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="n">
-        <v>0</v>
+        <v>0.62453125</v>
       </c>
     </row>
     <row r="434">
@@ -3917,7 +3917,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="n">
-        <v>0.84109375</v>
+        <v>0.3784375</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="n">
-        <v>0</v>
+        <v>0.4149999999999999</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="n">
-        <v>0.87484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.6428125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -3949,7 +3949,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="n">
-        <v>0.3714062499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -3965,7 +3965,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="n">
-        <v>0.955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -3973,7 +3973,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="n">
-        <v>0.90015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="n">
-        <v>0.9128125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -3997,7 +3997,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="n">
-        <v>0.5809375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="n">
-        <v>0.97328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -4013,7 +4013,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="n">
-        <v>0.7159375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="n">
-        <v>0</v>
+        <v>0.69203125</v>
       </c>
     </row>
     <row r="450">
@@ -4037,7 +4037,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="n">
-        <v>0.8565625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="n">
-        <v>0.5809375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -4061,7 +4061,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="n">
-        <v>0.791875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0</v>
+        <v>0.4178125</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="n">
-        <v>0.6737500000000001</v>
+        <v>0.61890625</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="n">
-        <v>0.9746875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -4117,7 +4117,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0</v>
+        <v>0.8565625</v>
       </c>
     </row>
     <row r="462">
@@ -4149,7 +4149,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="n">
-        <v>0.82140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -4173,7 +4173,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="n">
-        <v>0.6751562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="n">
-        <v>0.8790625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -4189,7 +4189,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="n">
-        <v>0.775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -4205,7 +4205,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>0.92125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="n">
-        <v>0.8003125</v>
+        <v>0.54859375</v>
       </c>
     </row>
     <row r="474">
@@ -4237,7 +4237,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="n">
-        <v>0.4037500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -4253,7 +4253,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="n">
-        <v>0.9254687500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -4261,7 +4261,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>0.95640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -4285,7 +4285,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="n">
-        <v>0.9521875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -4301,7 +4301,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>0.4149999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485">
@@ -4317,7 +4317,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="n">
-        <v>0.9465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -4333,7 +4333,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="n">
-        <v>0.6203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489">
@@ -4357,7 +4357,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="n">
-        <v>0</v>
+        <v>0.5809375</v>
       </c>
     </row>
     <row r="492">
@@ -4373,7 +4373,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="n">
-        <v>0.735625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -4381,7 +4381,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="n">
-        <v>0.52046875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495">
@@ -4405,7 +4405,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="n">
-        <v>0</v>
+        <v>0.7496875000000001</v>
       </c>
     </row>
     <row r="498">
@@ -4413,7 +4413,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>0.96765625</v>
+        <v>0.73703125</v>
       </c>
     </row>
     <row r="499">
@@ -4421,7 +4421,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>0.5809375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -4437,7 +4437,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="n">
-        <v>0.9339062499999999</v>
+        <v>0.8453125</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="n">
-        <v>0</v>
+        <v>0.5401562499999999</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="n">
-        <v>0.79609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -4461,7 +4461,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="n">
-        <v>0</v>
+        <v>0.39390625</v>
       </c>
     </row>
     <row r="505">
@@ -4477,7 +4477,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="n">
-        <v>0.41359375</v>
+        <v>0.90859375</v>
       </c>
     </row>
     <row r="507">
@@ -4509,7 +4509,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="n">
-        <v>0.6231249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511">
@@ -4517,7 +4517,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="n">
-        <v>0.6048437499999999</v>
+        <v>0.39109375</v>
       </c>
     </row>
     <row r="512">
@@ -4533,7 +4533,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="n">
-        <v>0</v>
+        <v>0.5443750000000001</v>
       </c>
     </row>
     <row r="514">
@@ -4549,7 +4549,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="n">
-        <v>0.66390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516">
@@ -4557,7 +4557,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="n">
-        <v>0.7553125000000001</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="517">
@@ -4581,7 +4581,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>0</v>
+        <v>0.8959375000000001</v>
       </c>
     </row>
     <row r="520">
@@ -4597,7 +4597,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>0</v>
+        <v>0.7581249999999999</v>
       </c>
     </row>
     <row r="522">
@@ -4605,7 +4605,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>0.74265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
@@ -4637,7 +4637,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="n">
-        <v>0.6034375000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -4645,7 +4645,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="n">
-        <v>0.7778125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
@@ -4653,7 +4653,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="n">
-        <v>0.83265625</v>
+        <v>0.40796875</v>
       </c>
     </row>
     <row r="529">
@@ -4661,7 +4661,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="n">
-        <v>0.32078125</v>
+        <v>0.7609375</v>
       </c>
     </row>
     <row r="530">
@@ -4669,7 +4669,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="531">
@@ -4677,7 +4677,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="n">
-        <v>0.65125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">
@@ -4693,7 +4693,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="n">
-        <v>0.8607812500000001</v>
+        <v>0.5823437499999999</v>
       </c>
     </row>
     <row r="534">
@@ -4701,7 +4701,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>0</v>
+        <v>0.836875</v>
       </c>
     </row>
     <row r="535">
@@ -4709,7 +4709,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="n">
-        <v>0</v>
+        <v>0.47828125</v>
       </c>
     </row>
     <row r="536">
@@ -4725,7 +4725,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="n">
-        <v>0</v>
+        <v>0.4853124999999999</v>
       </c>
     </row>
     <row r="538">
@@ -4733,7 +4733,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="n">
-        <v>0</v>
+        <v>0.5584375</v>
       </c>
     </row>
     <row r="539">
@@ -4749,7 +4749,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="n">
-        <v>0.386875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -4765,7 +4765,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>0.6498437500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -4781,7 +4781,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="n">
-        <v>0.47265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -4789,7 +4789,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="n">
-        <v>0.40515625</v>
+        <v>0.4712499999999999</v>
       </c>
     </row>
     <row r="546">
@@ -4797,7 +4797,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="n">
-        <v>0.3685937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -4805,7 +4805,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="n">
-        <v>0.5303125</v>
+        <v>0.6146875000000001</v>
       </c>
     </row>
     <row r="548">
@@ -4813,7 +4813,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="n">
-        <v>0</v>
+        <v>0.31796875</v>
       </c>
     </row>
     <row r="549">
@@ -4829,7 +4829,7 @@
         <v>549</v>
       </c>
       <c r="B550" t="n">
-        <v>0.71875</v>
+        <v>0.7398437499999999</v>
       </c>
     </row>
     <row r="551">
@@ -4837,7 +4837,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="n">
-        <v>0</v>
+        <v>0.59359375</v>
       </c>
     </row>
     <row r="552">
@@ -4861,7 +4861,7 @@
         <v>553</v>
       </c>
       <c r="B554" t="n">
-        <v>0.3714062499999999</v>
+        <v>0.780625</v>
       </c>
     </row>
     <row r="555">
@@ -4877,7 +4877,7 @@
         <v>555</v>
       </c>
       <c r="B556" t="n">
-        <v>0</v>
+        <v>0.5640624999999999</v>
       </c>
     </row>
     <row r="557">
@@ -4893,7 +4893,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>0.8692187499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -4901,7 +4901,7 @@
         <v>558</v>
       </c>
       <c r="B559" t="n">
-        <v>0.78484375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -4909,7 +4909,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>0.8396875</v>
+        <v>0.7215625</v>
       </c>
     </row>
     <row r="561">
@@ -4917,7 +4917,7 @@
         <v>560</v>
       </c>
       <c r="B561" t="n">
-        <v>0.713125</v>
+        <v>0.85234375</v>
       </c>
     </row>
     <row r="562">
@@ -4925,7 +4925,7 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>0</v>
+        <v>0.53171875</v>
       </c>
     </row>
     <row r="563">
@@ -4933,7 +4933,7 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0.60765625</v>
+        <v>0.49515625</v>
       </c>
     </row>
     <row r="564">
@@ -4941,7 +4941,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0.3728125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565">
@@ -4957,7 +4957,7 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>0.3278125000000001</v>
+        <v>0.9339062499999999</v>
       </c>
     </row>
     <row r="567">
@@ -4965,7 +4965,7 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>0.40515625</v>
+        <v>0.66671875</v>
       </c>
     </row>
     <row r="568">
@@ -4973,7 +4973,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0.82984375</v>
+        <v>0.5190625</v>
       </c>
     </row>
     <row r="569">
@@ -4981,7 +4981,7 @@
         <v>568</v>
       </c>
       <c r="B569" t="n">
-        <v>0.8903125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -4989,7 +4989,7 @@
         <v>569</v>
       </c>
       <c r="B570" t="n">
-        <v>0.5457812500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="571">
@@ -4997,7 +4997,7 @@
         <v>570</v>
       </c>
       <c r="B571" t="n">
-        <v>0.7581249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572">
@@ -5005,7 +5005,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>0.8790625</v>
+        <v>0.74125</v>
       </c>
     </row>
     <row r="573">
@@ -5021,7 +5021,7 @@
         <v>573</v>
       </c>
       <c r="B574" t="n">
-        <v>0</v>
+        <v>0.75390625</v>
       </c>
     </row>
     <row r="575">
@@ -5037,7 +5037,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0</v>
+        <v>0.62453125</v>
       </c>
     </row>
     <row r="577">
@@ -5053,7 +5053,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>0.6048437499999999</v>
+        <v>0.488125</v>
       </c>
     </row>
     <row r="579">
@@ -5061,7 +5061,7 @@
         <v>578</v>
       </c>
       <c r="B579" t="n">
-        <v>0.5879687499999999</v>
+        <v>0.8621875</v>
       </c>
     </row>
     <row r="580">
@@ -5077,7 +5077,7 @@
         <v>580</v>
       </c>
       <c r="B581" t="n">
-        <v>0.5528124999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
@@ -5117,7 +5117,7 @@
         <v>585</v>
       </c>
       <c r="B586" t="n">
-        <v>0.9128125</v>
+        <v>0.5640624999999999</v>
       </c>
     </row>
     <row r="587">
@@ -5125,7 +5125,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0.7581249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -5133,7 +5133,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0.84671875</v>
+        <v>0.8171875</v>
       </c>
     </row>
     <row r="589">
@@ -5149,7 +5149,7 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>0</v>
+        <v>0.6737500000000001</v>
       </c>
     </row>
     <row r="591">
@@ -5173,7 +5173,7 @@
         <v>592</v>
       </c>
       <c r="B593" t="n">
-        <v>0</v>
+        <v>0.83546875</v>
       </c>
     </row>
     <row r="594">
@@ -5189,7 +5189,7 @@
         <v>594</v>
       </c>
       <c r="B595" t="n">
-        <v>0</v>
+        <v>0.80453125</v>
       </c>
     </row>
     <row r="596">
@@ -5197,7 +5197,7 @@
         <v>595</v>
       </c>
       <c r="B596" t="n">
-        <v>0.724375</v>
+        <v>0.78484375</v>
       </c>
     </row>
     <row r="597">
@@ -5205,7 +5205,7 @@
         <v>596</v>
       </c>
       <c r="B597" t="n">
-        <v>0</v>
+        <v>0.2982812500000001</v>
       </c>
     </row>
     <row r="598">
@@ -5213,7 +5213,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>0</v>
+        <v>0.69765625</v>
       </c>
     </row>
     <row r="599">
@@ -5221,7 +5221,7 @@
         <v>598</v>
       </c>
       <c r="B599" t="n">
-        <v>0</v>
+        <v>0.6315625</v>
       </c>
     </row>
     <row r="600">
@@ -5229,7 +5229,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>0.949375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
@@ -5237,7 +5237,7 @@
         <v>600</v>
       </c>
       <c r="B601" t="n">
-        <v>0</v>
+        <v>0.769375</v>
       </c>
     </row>
     <row r="602">
@@ -5245,7 +5245,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0.9465625</v>
+        <v>0.38265625</v>
       </c>
     </row>
     <row r="603">
@@ -5253,7 +5253,7 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0</v>
+        <v>0.39109375</v>
       </c>
     </row>
     <row r="604">
@@ -5261,7 +5261,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>0.690625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="605">
@@ -5269,7 +5269,7 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0.8256250000000001</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="606">
@@ -5277,7 +5277,7 @@
         <v>605</v>
       </c>
       <c r="B606" t="n">
-        <v>0</v>
+        <v>0.7932812499999999</v>
       </c>
     </row>
     <row r="607">
@@ -5285,7 +5285,7 @@
         <v>606</v>
       </c>
       <c r="B607" t="n">
-        <v>0</v>
+        <v>0.40515625</v>
       </c>
     </row>
     <row r="608">
@@ -5301,7 +5301,7 @@
         <v>608</v>
       </c>
       <c r="B609" t="n">
-        <v>0</v>
+        <v>0.555625</v>
       </c>
     </row>
     <row r="610">
@@ -5309,7 +5309,7 @@
         <v>609</v>
       </c>
       <c r="B610" t="n">
-        <v>0.77078125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -5317,7 +5317,7 @@
         <v>610</v>
       </c>
       <c r="B611" t="n">
-        <v>0</v>
+        <v>0.5682812500000001</v>
       </c>
     </row>
     <row r="612">
@@ -5325,7 +5325,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>0</v>
+        <v>0.73421875</v>
       </c>
     </row>
     <row r="613">
@@ -5333,7 +5333,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0.6695312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -5341,7 +5341,7 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>0</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="615">
@@ -5357,7 +5357,7 @@
         <v>615</v>
       </c>
       <c r="B616" t="n">
-        <v>0.91984375</v>
+        <v>0.61046875</v>
       </c>
     </row>
     <row r="617">
@@ -5365,7 +5365,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>0</v>
+        <v>0.803125</v>
       </c>
     </row>
     <row r="618">
@@ -5373,7 +5373,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>0</v>
+        <v>0.735625</v>
       </c>
     </row>
     <row r="619">
@@ -5381,7 +5381,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>0.97046875</v>
+        <v>0.848125</v>
       </c>
     </row>
     <row r="620">
@@ -5389,7 +5389,7 @@
         <v>619</v>
       </c>
       <c r="B620" t="n">
-        <v>0</v>
+        <v>0.67796875</v>
       </c>
     </row>
     <row r="621">
@@ -5397,7 +5397,7 @@
         <v>620</v>
       </c>
       <c r="B621" t="n">
-        <v>0.6343749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -5405,7 +5405,7 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0</v>
+        <v>0.4796874999999999</v>
       </c>
     </row>
     <row r="623">
@@ -5413,7 +5413,7 @@
         <v>622</v>
       </c>
       <c r="B623" t="n">
-        <v>0</v>
+        <v>0.9282812499999999</v>
       </c>
     </row>
     <row r="624">
@@ -5421,7 +5421,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0.59640625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
@@ -5429,7 +5429,7 @@
         <v>624</v>
       </c>
       <c r="B625" t="n">
-        <v>0.7975</v>
+        <v>0.566875</v>
       </c>
     </row>
     <row r="626">
@@ -5437,7 +5437,7 @@
         <v>625</v>
       </c>
       <c r="B626" t="n">
-        <v>0.91703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
@@ -5453,7 +5453,7 @@
         <v>627</v>
       </c>
       <c r="B628" t="n">
-        <v>0.9254687500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629">
@@ -5461,7 +5461,7 @@
         <v>628</v>
       </c>
       <c r="B629" t="n">
-        <v>0</v>
+        <v>0.88328125</v>
       </c>
     </row>
     <row r="630">
@@ -5469,7 +5469,7 @@
         <v>629</v>
       </c>
       <c r="B630" t="n">
-        <v>0.600625</v>
+        <v>0.92265625</v>
       </c>
     </row>
     <row r="631">
@@ -5477,7 +5477,7 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>0.63015625</v>
+        <v>0.7989062499999999</v>
       </c>
     </row>
     <row r="632">
@@ -5493,7 +5493,7 @@
         <v>632</v>
       </c>
       <c r="B633" t="n">
-        <v>0.89734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -5501,7 +5501,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>0.8171875</v>
+        <v>0.60625</v>
       </c>
     </row>
     <row r="635">
@@ -5509,7 +5509,7 @@
         <v>634</v>
       </c>
       <c r="B635" t="n">
-        <v>0.8284374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
@@ -5517,7 +5517,7 @@
         <v>635</v>
       </c>
       <c r="B636" t="n">
-        <v>0.88046875</v>
+        <v>0.319375</v>
       </c>
     </row>
     <row r="637">
@@ -5525,7 +5525,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>0.9690625</v>
+        <v>0.6709375</v>
       </c>
     </row>
     <row r="638">
@@ -5533,7 +5533,7 @@
         <v>637</v>
       </c>
       <c r="B638" t="n">
-        <v>0.8903125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="639">
@@ -5541,7 +5541,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0.90859375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -5557,7 +5557,7 @@
         <v>640</v>
       </c>
       <c r="B641" t="n">
-        <v>0.9746875</v>
+        <v>0.85515625</v>
       </c>
     </row>
     <row r="642">
@@ -5565,7 +5565,7 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0.7904687500000001</v>
+        <v>0.5457812500000001</v>
       </c>
     </row>
     <row r="643">
@@ -5573,7 +5573,7 @@
         <v>642</v>
       </c>
       <c r="B643" t="n">
-        <v>0.7440625000000001</v>
+        <v>0.89171875</v>
       </c>
     </row>
     <row r="644">
@@ -5581,7 +5581,7 @@
         <v>643</v>
       </c>
       <c r="B644" t="n">
-        <v>0.94796875</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="645">
@@ -5597,7 +5597,7 @@
         <v>645</v>
       </c>
       <c r="B646" t="n">
-        <v>0.9015625</v>
+        <v>0.3896875</v>
       </c>
     </row>
     <row r="647">
@@ -5605,7 +5605,7 @@
         <v>646</v>
       </c>
       <c r="B647" t="n">
-        <v>0.91703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="648">
@@ -5613,7 +5613,7 @@
         <v>647</v>
       </c>
       <c r="B648" t="n">
-        <v>0.49515625</v>
+        <v>0.319375</v>
       </c>
     </row>
     <row r="649">
@@ -5621,7 +5621,7 @@
         <v>648</v>
       </c>
       <c r="B649" t="n">
-        <v>0.75953125</v>
+        <v>0.8734375</v>
       </c>
     </row>
     <row r="650">
@@ -5629,7 +5629,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>0.9859375</v>
+        <v>0.45296875</v>
       </c>
     </row>
     <row r="651">
@@ -5637,7 +5637,7 @@
         <v>650</v>
       </c>
       <c r="B651" t="n">
-        <v>0.97609375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652">
@@ -5645,7 +5645,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>0.5879687499999999</v>
+        <v>0.7285937499999999</v>
       </c>
     </row>
     <row r="653">
@@ -5653,7 +5653,7 @@
         <v>652</v>
       </c>
       <c r="B653" t="n">
-        <v>0</v>
+        <v>0.4571875</v>
       </c>
     </row>
     <row r="654">
@@ -5669,7 +5669,7 @@
         <v>654</v>
       </c>
       <c r="B655" t="n">
-        <v>0.78484375</v>
+        <v>0.6399999999999999</v>
       </c>
     </row>
     <row r="656">
@@ -5677,7 +5677,7 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>0.91140625</v>
+        <v>0.7173437499999999</v>
       </c>
     </row>
     <row r="657">
@@ -5693,7 +5693,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0</v>
+        <v>0.52609375</v>
       </c>
     </row>
     <row r="659">
@@ -5701,7 +5701,7 @@
         <v>658</v>
       </c>
       <c r="B659" t="n">
-        <v>0.91703125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -5709,7 +5709,7 @@
         <v>659</v>
       </c>
       <c r="B660" t="n">
-        <v>0.94515625</v>
+        <v>0.6582812499999999</v>
       </c>
     </row>
     <row r="661">
@@ -5717,7 +5717,7 @@
         <v>660</v>
       </c>
       <c r="B661" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="662">
@@ -5725,7 +5725,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0.5035937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
@@ -5733,7 +5733,7 @@
         <v>662</v>
       </c>
       <c r="B663" t="n">
-        <v>0.325</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="664">
@@ -5741,7 +5741,7 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0.4121875</v>
+        <v>0.780625</v>
       </c>
     </row>
     <row r="665">
@@ -5749,7 +5749,7 @@
         <v>664</v>
       </c>
       <c r="B665" t="n">
-        <v>0.91140625</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="666">
@@ -5757,7 +5757,7 @@
         <v>665</v>
       </c>
       <c r="B666" t="n">
-        <v>0</v>
+        <v>0.90296875</v>
       </c>
     </row>
     <row r="667">
@@ -5765,7 +5765,7 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>0.85375</v>
+        <v>0.59078125</v>
       </c>
     </row>
     <row r="668">
@@ -5773,7 +5773,7 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0.915625</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="669">
@@ -5781,7 +5781,7 @@
         <v>668</v>
       </c>
       <c r="B669" t="n">
-        <v>0</v>
+        <v>0.6709375</v>
       </c>
     </row>
     <row r="670">
@@ -5797,7 +5797,7 @@
         <v>670</v>
       </c>
       <c r="B671" t="n">
-        <v>0.8875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
@@ -5805,7 +5805,7 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0.93671875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="673">
@@ -5813,7 +5813,7 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="674">
@@ -5821,7 +5821,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0</v>
+        <v>0.7792187500000001</v>
       </c>
     </row>
     <row r="675">
@@ -5829,7 +5829,7 @@
         <v>674</v>
       </c>
       <c r="B675" t="n">
-        <v>0.6259375</v>
+        <v>0.8495312500000001</v>
       </c>
     </row>
     <row r="676">
@@ -5837,7 +5837,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>0</v>
+        <v>0.33484375</v>
       </c>
     </row>
     <row r="677">
@@ -5845,7 +5845,7 @@
         <v>676</v>
       </c>
       <c r="B677" t="n">
-        <v>0.44734375</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="678">
@@ -5853,7 +5853,7 @@
         <v>677</v>
       </c>
       <c r="B678" t="n">
-        <v>0.77359375</v>
+        <v>0.8396875</v>
       </c>
     </row>
     <row r="679">
@@ -5861,7 +5861,7 @@
         <v>678</v>
       </c>
       <c r="B679" t="n">
-        <v>0</v>
+        <v>0.7890625</v>
       </c>
     </row>
     <row r="680">
@@ -5877,7 +5877,7 @@
         <v>680</v>
       </c>
       <c r="B681" t="n">
-        <v>0</v>
+        <v>0.95078125</v>
       </c>
     </row>
     <row r="682">
@@ -5893,7 +5893,7 @@
         <v>682</v>
       </c>
       <c r="B683" t="n">
-        <v>0</v>
+        <v>0.85234375</v>
       </c>
     </row>
     <row r="684">
@@ -5901,7 +5901,7 @@
         <v>683</v>
       </c>
       <c r="B684" t="n">
-        <v>0</v>
+        <v>0.7792187500000001</v>
       </c>
     </row>
     <row r="685">
@@ -5909,7 +5909,7 @@
         <v>684</v>
       </c>
       <c r="B685" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.8959375000000001</v>
       </c>
     </row>
     <row r="686">
@@ -5917,7 +5917,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.97890625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -5925,7 +5925,7 @@
         <v>686</v>
       </c>
       <c r="B687" t="n">
-        <v>0</v>
+        <v>0.5471874999999999</v>
       </c>
     </row>
     <row r="688">
@@ -5933,7 +5933,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>0.8425</v>
+        <v>0.77359375</v>
       </c>
     </row>
     <row r="689">
@@ -5941,7 +5941,7 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>0.97328125</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="690">
@@ -5949,7 +5949,7 @@
         <v>689</v>
       </c>
       <c r="B690" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="691">
@@ -5957,7 +5957,7 @@
         <v>690</v>
       </c>
       <c r="B691" t="n">
-        <v>0.8509375</v>
+        <v>0.7778125</v>
       </c>
     </row>
     <row r="692">
@@ -5965,7 +5965,7 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>0</v>
+        <v>0.31375</v>
       </c>
     </row>
     <row r="693">
@@ -5973,7 +5973,7 @@
         <v>692</v>
       </c>
       <c r="B693" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="694">
@@ -5989,7 +5989,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.325</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="696">
@@ -5997,7 +5997,7 @@
         <v>695</v>
       </c>
       <c r="B696" t="n">
-        <v>0</v>
+        <v>0.6821874999999999</v>
       </c>
     </row>
     <row r="697">
@@ -6005,7 +6005,7 @@
         <v>696</v>
       </c>
       <c r="B697" t="n">
-        <v>0.85234375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="698">
@@ -6029,7 +6029,7 @@
         <v>699</v>
       </c>
       <c r="B700" t="n">
-        <v>0.47546875</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="701">
@@ -6037,7 +6037,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>0</v>
+        <v>0.38125</v>
       </c>
     </row>
     <row r="702">
@@ -6045,7 +6045,7 @@
         <v>701</v>
       </c>
       <c r="B702" t="n">
-        <v>0.40234375</v>
+        <v>0.85375</v>
       </c>
     </row>
     <row r="703">
@@ -6053,7 +6053,7 @@
         <v>702</v>
       </c>
       <c r="B703" t="n">
-        <v>0.75953125</v>
+        <v>0.881875</v>
       </c>
     </row>
     <row r="704">
@@ -6061,7 +6061,7 @@
         <v>703</v>
       </c>
       <c r="B704" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="705">
@@ -6069,7 +6069,7 @@
         <v>704</v>
       </c>
       <c r="B705" t="n">
-        <v>0.89453125</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="706">
@@ -6077,7 +6077,7 @@
         <v>705</v>
       </c>
       <c r="B706" t="n">
-        <v>0.98171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -6085,7 +6085,7 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>0.9746875</v>
+        <v>0.8228124999999999</v>
       </c>
     </row>
     <row r="708">
@@ -6093,7 +6093,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>0</v>
+        <v>0.3657812499999999</v>
       </c>
     </row>
     <row r="709">
@@ -6101,7 +6101,7 @@
         <v>708</v>
       </c>
       <c r="B709" t="n">
-        <v>0</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="710">
@@ -6109,7 +6109,7 @@
         <v>709</v>
       </c>
       <c r="B710" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="711">
@@ -6117,7 +6117,7 @@
         <v>710</v>
       </c>
       <c r="B711" t="n">
-        <v>0.3840625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712">
@@ -6125,7 +6125,7 @@
         <v>711</v>
       </c>
       <c r="B712" t="n">
-        <v>0.83125</v>
+        <v>0.91421875</v>
       </c>
     </row>
     <row r="713">
@@ -6133,7 +6133,7 @@
         <v>712</v>
       </c>
       <c r="B713" t="n">
-        <v>0</v>
+        <v>0.8143750000000001</v>
       </c>
     </row>
     <row r="714">
@@ -6141,7 +6141,7 @@
         <v>713</v>
       </c>
       <c r="B714" t="n">
-        <v>0.8340624999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -6157,7 +6157,7 @@
         <v>715</v>
       </c>
       <c r="B716" t="n">
-        <v>0</v>
+        <v>0.8059375</v>
       </c>
     </row>
     <row r="717">
@@ -6165,7 +6165,7 @@
         <v>716</v>
       </c>
       <c r="B717" t="n">
-        <v>0</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="718">
@@ -6173,7 +6173,7 @@
         <v>717</v>
       </c>
       <c r="B718" t="n">
-        <v>0</v>
+        <v>0.9015625</v>
       </c>
     </row>
     <row r="719">
@@ -6181,7 +6181,7 @@
         <v>718</v>
       </c>
       <c r="B719" t="n">
-        <v>0.3278125000000001</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="720">
@@ -6197,7 +6197,7 @@
         <v>720</v>
       </c>
       <c r="B721" t="n">
-        <v>0</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="722">
@@ -6205,7 +6205,7 @@
         <v>721</v>
       </c>
       <c r="B722" t="n">
-        <v>0.595</v>
+        <v>0.87203125</v>
       </c>
     </row>
     <row r="723">
@@ -6213,7 +6213,7 @@
         <v>722</v>
       </c>
       <c r="B723" t="n">
-        <v>0</v>
+        <v>0.83265625</v>
       </c>
     </row>
     <row r="724">
@@ -6221,7 +6221,7 @@
         <v>723</v>
       </c>
       <c r="B724" t="n">
-        <v>0.5289062499999999</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="725">
@@ -6229,7 +6229,7 @@
         <v>724</v>
       </c>
       <c r="B725" t="n">
-        <v>0.6090625000000001</v>
+        <v>0.83546875</v>
       </c>
     </row>
     <row r="726">
@@ -6245,7 +6245,7 @@
         <v>726</v>
       </c>
       <c r="B727" t="n">
-        <v>0</v>
+        <v>0.6878124999999999</v>
       </c>
     </row>
     <row r="728">
@@ -6261,7 +6261,7 @@
         <v>728</v>
       </c>
       <c r="B729" t="n">
-        <v>0.8003125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730">
@@ -6269,7 +6269,7 @@
         <v>729</v>
       </c>
       <c r="B730" t="n">
-        <v>0</v>
+        <v>0.8635937499999999</v>
       </c>
     </row>
     <row r="731">
@@ -6277,7 +6277,7 @@
         <v>730</v>
       </c>
       <c r="B731" t="n">
-        <v>0.7637499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="732">
@@ -6285,7 +6285,7 @@
         <v>731</v>
       </c>
       <c r="B732" t="n">
-        <v>0</v>
+        <v>0.71171875</v>
       </c>
     </row>
     <row r="733">
@@ -6293,7 +6293,7 @@
         <v>732</v>
       </c>
       <c r="B733" t="n">
-        <v>0.6484375</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="734">
@@ -6301,7 +6301,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>0</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="735">
@@ -6309,7 +6309,7 @@
         <v>734</v>
       </c>
       <c r="B735" t="n">
-        <v>0</v>
+        <v>0.9465625</v>
       </c>
     </row>
     <row r="736">
@@ -6317,7 +6317,7 @@
         <v>735</v>
       </c>
       <c r="B736" t="n">
-        <v>0</v>
+        <v>0.54859375</v>
       </c>
     </row>
     <row r="737">
@@ -6325,7 +6325,7 @@
         <v>736</v>
       </c>
       <c r="B737" t="n">
-        <v>0.3615625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="738">
@@ -6333,7 +6333,7 @@
         <v>737</v>
       </c>
       <c r="B738" t="n">
-        <v>0.35734375</v>
+        <v>0.7932812499999999</v>
       </c>
     </row>
     <row r="739">
@@ -6341,7 +6341,7 @@
         <v>738</v>
       </c>
       <c r="B739" t="n">
-        <v>0</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="740">
@@ -6349,7 +6349,7 @@
         <v>739</v>
       </c>
       <c r="B740" t="n">
-        <v>0.57109375</v>
+        <v>0.70046875</v>
       </c>
     </row>
     <row r="741">
@@ -6357,7 +6357,7 @@
         <v>740</v>
       </c>
       <c r="B741" t="n">
-        <v>0.78203125</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="742">
@@ -6365,7 +6365,7 @@
         <v>741</v>
       </c>
       <c r="B742" t="n">
-        <v>0.6442187500000001</v>
+        <v>0.6470312499999999</v>
       </c>
     </row>
     <row r="743">
@@ -6373,7 +6373,7 @@
         <v>742</v>
       </c>
       <c r="B743" t="n">
-        <v>0.5120312499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
@@ -6397,7 +6397,7 @@
         <v>745</v>
       </c>
       <c r="B746" t="n">
-        <v>0</v>
+        <v>0.7876562499999999</v>
       </c>
     </row>
     <row r="747">
@@ -6405,7 +6405,7 @@
         <v>746</v>
       </c>
       <c r="B747" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="748">
@@ -6413,7 +6413,7 @@
         <v>747</v>
       </c>
       <c r="B748" t="n">
-        <v>0.94515625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="749">
@@ -6421,7 +6421,7 @@
         <v>748</v>
       </c>
       <c r="B749" t="n">
-        <v>0</v>
+        <v>0.8340624999999999</v>
       </c>
     </row>
     <row r="750">
@@ -6437,7 +6437,7 @@
         <v>750</v>
       </c>
       <c r="B751" t="n">
-        <v>0</v>
+        <v>0.94375</v>
       </c>
     </row>
     <row r="752">
@@ -6445,7 +6445,7 @@
         <v>751</v>
       </c>
       <c r="B752" t="n">
-        <v>0.7046874999999999</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="753">
@@ -6453,7 +6453,7 @@
         <v>752</v>
       </c>
       <c r="B753" t="n">
-        <v>0</v>
+        <v>0.7609375</v>
       </c>
     </row>
     <row r="754">
@@ -6469,7 +6469,7 @@
         <v>754</v>
       </c>
       <c r="B755" t="n">
-        <v>0.9465625</v>
+        <v>0.63296875</v>
       </c>
     </row>
     <row r="756">
@@ -6477,7 +6477,7 @@
         <v>755</v>
       </c>
       <c r="B756" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="757">
@@ -6493,7 +6493,7 @@
         <v>757</v>
       </c>
       <c r="B758" t="n">
-        <v>0</v>
+        <v>0.87625</v>
       </c>
     </row>
     <row r="759">
@@ -6501,7 +6501,7 @@
         <v>758</v>
       </c>
       <c r="B759" t="n">
-        <v>0</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="760">
@@ -6517,7 +6517,7 @@
         <v>760</v>
       </c>
       <c r="B761" t="n">
-        <v>0</v>
+        <v>0.94375</v>
       </c>
     </row>
     <row r="762">
@@ -6525,7 +6525,7 @@
         <v>761</v>
       </c>
       <c r="B762" t="n">
-        <v>0.4515625</v>
+        <v>0.7876562499999999</v>
       </c>
     </row>
     <row r="763">
@@ -6533,7 +6533,7 @@
         <v>762</v>
       </c>
       <c r="B763" t="n">
-        <v>0</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="764">
@@ -6549,7 +6549,7 @@
         <v>764</v>
       </c>
       <c r="B765" t="n">
-        <v>0.61609375</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="766">
@@ -6565,7 +6565,7 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>0</v>
+        <v>0.91140625</v>
       </c>
     </row>
     <row r="768">
@@ -6573,7 +6573,7 @@
         <v>767</v>
       </c>
       <c r="B768" t="n">
-        <v>0.36015625</v>
+        <v>0.74265625</v>
       </c>
     </row>
     <row r="769">
@@ -6581,7 +6581,7 @@
         <v>768</v>
       </c>
       <c r="B769" t="n">
-        <v>0</v>
+        <v>0.5443750000000001</v>
       </c>
     </row>
     <row r="770">
@@ -6589,7 +6589,7 @@
         <v>769</v>
       </c>
       <c r="B770" t="n">
-        <v>0</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="771">
@@ -6597,7 +6597,7 @@
         <v>770</v>
       </c>
       <c r="B771" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="772">
@@ -6605,7 +6605,7 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>0</v>
+        <v>0.9634374999999999</v>
       </c>
     </row>
     <row r="773">
@@ -6621,7 +6621,7 @@
         <v>773</v>
       </c>
       <c r="B774" t="n">
-        <v>0</v>
+        <v>0.9240625</v>
       </c>
     </row>
     <row r="775">
@@ -6629,7 +6629,7 @@
         <v>774</v>
       </c>
       <c r="B775" t="n">
-        <v>0</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="776">
@@ -6637,7 +6637,7 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>0.5289062499999999</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="777">
@@ -6645,7 +6645,7 @@
         <v>776</v>
       </c>
       <c r="B777" t="n">
-        <v>0</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="778">
@@ -6653,7 +6653,7 @@
         <v>777</v>
       </c>
       <c r="B778" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="779">
@@ -6661,7 +6661,7 @@
         <v>778</v>
       </c>
       <c r="B779" t="n">
-        <v>0.47546875</v>
+        <v>0.5387500000000001</v>
       </c>
     </row>
     <row r="780">
@@ -6669,7 +6669,7 @@
         <v>779</v>
       </c>
       <c r="B780" t="n">
-        <v>0.9015625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="781">
@@ -6677,7 +6677,7 @@
         <v>780</v>
       </c>
       <c r="B781" t="n">
-        <v>0</v>
+        <v>0.96765625</v>
       </c>
     </row>
     <row r="782">
@@ -6685,7 +6685,7 @@
         <v>781</v>
       </c>
       <c r="B782" t="n">
-        <v>0.865</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="783">
@@ -6693,7 +6693,7 @@
         <v>782</v>
       </c>
       <c r="B783" t="n">
-        <v>0.8396875</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="784">
@@ -6701,7 +6701,7 @@
         <v>783</v>
       </c>
       <c r="B784" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="785">
@@ -6709,7 +6709,7 @@
         <v>784</v>
       </c>
       <c r="B785" t="n">
-        <v>0.6385937500000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="786">
@@ -6717,7 +6717,7 @@
         <v>785</v>
       </c>
       <c r="B786" t="n">
-        <v>0.8509375</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="787">
@@ -6725,7 +6725,7 @@
         <v>786</v>
       </c>
       <c r="B787" t="n">
-        <v>0.859375</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="788">
@@ -6741,7 +6741,7 @@
         <v>788</v>
       </c>
       <c r="B789" t="n">
-        <v>0</v>
+        <v>0.95078125</v>
       </c>
     </row>
     <row r="790">
@@ -6749,7 +6749,7 @@
         <v>789</v>
       </c>
       <c r="B790" t="n">
-        <v>0</v>
+        <v>0.9409375</v>
       </c>
     </row>
     <row r="791">
@@ -6765,7 +6765,7 @@
         <v>791</v>
       </c>
       <c r="B792" t="n">
-        <v>0</v>
+        <v>0.93671875</v>
       </c>
     </row>
     <row r="793">
@@ -6773,7 +6773,7 @@
         <v>792</v>
       </c>
       <c r="B793" t="n">
-        <v>0.296875</v>
+        <v>0.94234375</v>
       </c>
     </row>
     <row r="794">
@@ -6781,7 +6781,7 @@
         <v>793</v>
       </c>
       <c r="B794" t="n">
-        <v>0.319375</v>
+        <v>0.55984375</v>
       </c>
     </row>
     <row r="795">
@@ -6789,7 +6789,7 @@
         <v>794</v>
       </c>
       <c r="B795" t="n">
-        <v>0</v>
+        <v>0.39109375</v>
       </c>
     </row>
     <row r="796">
@@ -6797,7 +6797,7 @@
         <v>795</v>
       </c>
       <c r="B796" t="n">
-        <v>0</v>
+        <v>0.89453125</v>
       </c>
     </row>
     <row r="797">
@@ -6805,7 +6805,7 @@
         <v>796</v>
       </c>
       <c r="B797" t="n">
-        <v>0</v>
+        <v>0.91984375</v>
       </c>
     </row>
     <row r="798">
@@ -6813,7 +6813,7 @@
         <v>797</v>
       </c>
       <c r="B798" t="n">
-        <v>0</v>
+        <v>0.81296875</v>
       </c>
     </row>
     <row r="799">
@@ -6821,7 +6821,7 @@
         <v>798</v>
       </c>
       <c r="B799" t="n">
-        <v>0.80734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800">
@@ -6829,7 +6829,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.73421875</v>
+        <v>0.92125</v>
       </c>
     </row>
     <row r="801">
@@ -6837,7 +6837,7 @@
         <v>800</v>
       </c>
       <c r="B801" t="n">
-        <v>0.5640624999999999</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="802">
@@ -6845,7 +6845,7 @@
         <v>801</v>
       </c>
       <c r="B802" t="n">
-        <v>0</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="803">
@@ -6861,7 +6861,7 @@
         <v>803</v>
       </c>
       <c r="B804" t="n">
-        <v>0</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="805">
@@ -6877,7 +6877,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.7778125</v>
+        <v>0.6878124999999999</v>
       </c>
     </row>
     <row r="807">
@@ -6885,7 +6885,7 @@
         <v>806</v>
       </c>
       <c r="B807" t="n">
-        <v>0</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="808">
@@ -6893,7 +6893,7 @@
         <v>807</v>
       </c>
       <c r="B808" t="n">
-        <v>0</v>
+        <v>0.870625</v>
       </c>
     </row>
     <row r="809">
@@ -6901,7 +6901,7 @@
         <v>808</v>
       </c>
       <c r="B809" t="n">
-        <v>0.6540625</v>
+        <v>0.6315625</v>
       </c>
     </row>
     <row r="810">
@@ -6909,7 +6909,7 @@
         <v>809</v>
       </c>
       <c r="B810" t="n">
-        <v>0</v>
+        <v>0.9325</v>
       </c>
     </row>
     <row r="811">
@@ -6917,7 +6917,7 @@
         <v>810</v>
       </c>
       <c r="B811" t="n">
-        <v>0.488125</v>
+        <v>0.81859375</v>
       </c>
     </row>
     <row r="812">
@@ -6933,7 +6933,7 @@
         <v>812</v>
       </c>
       <c r="B813" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="814">
@@ -6941,7 +6941,7 @@
         <v>813</v>
       </c>
       <c r="B814" t="n">
-        <v>0</v>
+        <v>0.75671875</v>
       </c>
     </row>
     <row r="815">
@@ -6957,7 +6957,7 @@
         <v>815</v>
       </c>
       <c r="B816" t="n">
-        <v>0</v>
+        <v>0.870625</v>
       </c>
     </row>
     <row r="817">
@@ -6973,7 +6973,7 @@
         <v>817</v>
       </c>
       <c r="B818" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="819">
@@ -6981,7 +6981,7 @@
         <v>818</v>
       </c>
       <c r="B819" t="n">
-        <v>0</v>
+        <v>0.89734375</v>
       </c>
     </row>
     <row r="820">
@@ -6989,7 +6989,7 @@
         <v>819</v>
       </c>
       <c r="B820" t="n">
-        <v>0</v>
+        <v>0.7285937499999999</v>
       </c>
     </row>
     <row r="821">
@@ -6997,7 +6997,7 @@
         <v>820</v>
       </c>
       <c r="B821" t="n">
-        <v>0</v>
+        <v>0.9254687500000001</v>
       </c>
     </row>
     <row r="822">
@@ -7013,7 +7013,7 @@
         <v>822</v>
       </c>
       <c r="B823" t="n">
-        <v>0.6934374999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="824">
@@ -7021,7 +7021,7 @@
         <v>823</v>
       </c>
       <c r="B824" t="n">
-        <v>0</v>
+        <v>0.88609375</v>
       </c>
     </row>
     <row r="825">
@@ -7029,7 +7029,7 @@
         <v>824</v>
       </c>
       <c r="B825" t="n">
-        <v>0</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="826">
@@ -7037,7 +7037,7 @@
         <v>825</v>
       </c>
       <c r="B826" t="n">
-        <v>0</v>
+        <v>0.7778125</v>
       </c>
     </row>
     <row r="827">
@@ -7045,7 +7045,7 @@
         <v>826</v>
       </c>
       <c r="B827" t="n">
-        <v>0</v>
+        <v>0.88046875</v>
       </c>
     </row>
     <row r="828">
@@ -7053,7 +7053,7 @@
         <v>827</v>
       </c>
       <c r="B828" t="n">
-        <v>0</v>
+        <v>0.96203125</v>
       </c>
     </row>
     <row r="829">
@@ -7061,7 +7061,7 @@
         <v>828</v>
       </c>
       <c r="B829" t="n">
-        <v>0</v>
+        <v>0.8903125000000001</v>
       </c>
     </row>
     <row r="830">
@@ -7069,7 +7069,7 @@
         <v>829</v>
       </c>
       <c r="B830" t="n">
-        <v>0</v>
+        <v>0.8340624999999999</v>
       </c>
     </row>
     <row r="831">
@@ -7077,7 +7077,7 @@
         <v>830</v>
       </c>
       <c r="B831" t="n">
-        <v>0</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="832">
@@ -7085,7 +7085,7 @@
         <v>831</v>
       </c>
       <c r="B832" t="n">
-        <v>0.5106250000000001</v>
+        <v>0.5401562499999999</v>
       </c>
     </row>
     <row r="833">
@@ -7093,7 +7093,7 @@
         <v>832</v>
       </c>
       <c r="B833" t="n">
-        <v>0.7496875000000001</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="834">
@@ -7101,7 +7101,7 @@
         <v>833</v>
       </c>
       <c r="B834" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="835">
@@ -7117,7 +7117,7 @@
         <v>835</v>
       </c>
       <c r="B836" t="n">
-        <v>0</v>
+        <v>0.9254687500000001</v>
       </c>
     </row>
     <row r="837">
@@ -7149,7 +7149,7 @@
         <v>839</v>
       </c>
       <c r="B840" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="841">
@@ -7157,7 +7157,7 @@
         <v>840</v>
       </c>
       <c r="B841" t="n">
-        <v>0</v>
+        <v>0.9296875</v>
       </c>
     </row>
     <row r="842">
@@ -7165,7 +7165,7 @@
         <v>841</v>
       </c>
       <c r="B842" t="n">
-        <v>0</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="843">
@@ -7173,7 +7173,7 @@
         <v>842</v>
       </c>
       <c r="B843" t="n">
-        <v>0</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="844">
@@ -7181,7 +7181,7 @@
         <v>843</v>
       </c>
       <c r="B844" t="n">
-        <v>0</v>
+        <v>0.915625</v>
       </c>
     </row>
     <row r="845">
@@ -7189,7 +7189,7 @@
         <v>844</v>
       </c>
       <c r="B845" t="n">
-        <v>0.95640625</v>
+        <v>0.82984375</v>
       </c>
     </row>
     <row r="846">
@@ -7197,7 +7197,7 @@
         <v>845</v>
       </c>
       <c r="B846" t="n">
-        <v>0.61609375</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="847">
@@ -7205,7 +7205,7 @@
         <v>846</v>
       </c>
       <c r="B847" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="848">
@@ -7213,7 +7213,7 @@
         <v>847</v>
       </c>
       <c r="B848" t="n">
-        <v>0</v>
+        <v>0.95078125</v>
       </c>
     </row>
     <row r="849">
@@ -7237,7 +7237,7 @@
         <v>850</v>
       </c>
       <c r="B851" t="n">
-        <v>0</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="852">
@@ -7245,7 +7245,7 @@
         <v>851</v>
       </c>
       <c r="B852" t="n">
-        <v>0</v>
+        <v>0.904375</v>
       </c>
     </row>
     <row r="853">
@@ -7253,7 +7253,7 @@
         <v>852</v>
       </c>
       <c r="B853" t="n">
-        <v>0.5401562499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="854">
@@ -7269,7 +7269,7 @@
         <v>854</v>
       </c>
       <c r="B855" t="n">
-        <v>0</v>
+        <v>0.84109375</v>
       </c>
     </row>
     <row r="856">
@@ -7285,7 +7285,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="n">
-        <v>0</v>
+        <v>0.9521875</v>
       </c>
     </row>
     <row r="858">
@@ -7293,7 +7293,7 @@
         <v>857</v>
       </c>
       <c r="B858" t="n">
-        <v>0</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="859">
@@ -7309,7 +7309,7 @@
         <v>859</v>
       </c>
       <c r="B860" t="n">
-        <v>0</v>
+        <v>0.8931249999999999</v>
       </c>
     </row>
     <row r="861">
@@ -7317,7 +7317,7 @@
         <v>860</v>
       </c>
       <c r="B861" t="n">
-        <v>0.65546875</v>
+        <v>0.80453125</v>
       </c>
     </row>
     <row r="862">
@@ -7333,7 +7333,7 @@
         <v>862</v>
       </c>
       <c r="B863" t="n">
-        <v>0</v>
+        <v>0.9339062499999999</v>
       </c>
     </row>
     <row r="864">
@@ -7341,7 +7341,7 @@
         <v>863</v>
       </c>
       <c r="B864" t="n">
-        <v>0</v>
+        <v>0.70328125</v>
       </c>
     </row>
     <row r="865">
@@ -7349,7 +7349,7 @@
         <v>864</v>
       </c>
       <c r="B865" t="n">
-        <v>0.4796874999999999</v>
+        <v>0.9128125</v>
       </c>
     </row>
     <row r="866">
@@ -7365,7 +7365,7 @@
         <v>866</v>
       </c>
       <c r="B867" t="n">
-        <v>0</v>
+        <v>0.87765625</v>
       </c>
     </row>
     <row r="868">
@@ -7373,7 +7373,7 @@
         <v>867</v>
       </c>
       <c r="B868" t="n">
-        <v>0.32640625</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="869">
@@ -7381,7 +7381,7 @@
         <v>868</v>
       </c>
       <c r="B869" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="870">
@@ -7389,7 +7389,7 @@
         <v>869</v>
       </c>
       <c r="B870" t="n">
-        <v>0</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="871">
@@ -7405,7 +7405,7 @@
         <v>871</v>
       </c>
       <c r="B872" t="n">
-        <v>0</v>
+        <v>0.87484375</v>
       </c>
     </row>
     <row r="873">
@@ -7421,7 +7421,7 @@
         <v>873</v>
       </c>
       <c r="B874" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="875">
@@ -7429,7 +7429,7 @@
         <v>874</v>
       </c>
       <c r="B875" t="n">
-        <v>0</v>
+        <v>0.983125</v>
       </c>
     </row>
     <row r="876">
@@ -7437,7 +7437,7 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>0.7201562500000001</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="877">
@@ -7445,7 +7445,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>0.53171875</v>
+        <v>0.949375</v>
       </c>
     </row>
     <row r="878">
@@ -7453,7 +7453,7 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="879">
@@ -7461,7 +7461,7 @@
         <v>878</v>
       </c>
       <c r="B879" t="n">
-        <v>0</v>
+        <v>0.8903125000000001</v>
       </c>
     </row>
     <row r="880">
@@ -7477,7 +7477,7 @@
         <v>880</v>
       </c>
       <c r="B881" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="882">
@@ -7485,7 +7485,7 @@
         <v>881</v>
       </c>
       <c r="B882" t="n">
-        <v>0.7229687499999999</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="883">
@@ -7493,7 +7493,7 @@
         <v>882</v>
       </c>
       <c r="B883" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="884">
@@ -7501,7 +7501,7 @@
         <v>883</v>
       </c>
       <c r="B884" t="n">
-        <v>0</v>
+        <v>0.87484375</v>
       </c>
     </row>
     <row r="885">
@@ -7509,7 +7509,7 @@
         <v>884</v>
       </c>
       <c r="B885" t="n">
-        <v>0.50078125</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="886">
@@ -7517,7 +7517,7 @@
         <v>885</v>
       </c>
       <c r="B886" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="887">
@@ -7525,7 +7525,7 @@
         <v>886</v>
       </c>
       <c r="B887" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="888">
@@ -7533,7 +7533,7 @@
         <v>887</v>
       </c>
       <c r="B888" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="889">
@@ -7541,7 +7541,7 @@
         <v>888</v>
       </c>
       <c r="B889" t="n">
-        <v>0</v>
+        <v>0.971875</v>
       </c>
     </row>
     <row r="890">
@@ -7549,7 +7549,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>0</v>
+        <v>0.9310937500000001</v>
       </c>
     </row>
     <row r="891">
@@ -7557,7 +7557,7 @@
         <v>890</v>
       </c>
       <c r="B891" t="n">
-        <v>0</v>
+        <v>0.41640625</v>
       </c>
     </row>
     <row r="892">
@@ -7565,7 +7565,7 @@
         <v>891</v>
       </c>
       <c r="B892" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="893">
@@ -7573,7 +7573,7 @@
         <v>892</v>
       </c>
       <c r="B893" t="n">
-        <v>0.42625</v>
+        <v>0.88890625</v>
       </c>
     </row>
     <row r="894">
@@ -7581,7 +7581,7 @@
         <v>893</v>
       </c>
       <c r="B894" t="n">
-        <v>0</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="895">
@@ -7589,7 +7589,7 @@
         <v>894</v>
       </c>
       <c r="B895" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="896">
@@ -7597,7 +7597,7 @@
         <v>895</v>
       </c>
       <c r="B896" t="n">
-        <v>0.68640625</v>
+        <v>0.95359375</v>
       </c>
     </row>
     <row r="897">
@@ -7605,7 +7605,7 @@
         <v>896</v>
       </c>
       <c r="B897" t="n">
-        <v>0</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="898">
@@ -7613,7 +7613,7 @@
         <v>897</v>
       </c>
       <c r="B898" t="n">
-        <v>0</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="899">
@@ -7621,7 +7621,7 @@
         <v>898</v>
       </c>
       <c r="B899" t="n">
-        <v>0.4375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="900">
@@ -7629,7 +7629,7 @@
         <v>899</v>
       </c>
       <c r="B900" t="n">
-        <v>0.4965625</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="901">
@@ -7637,7 +7637,7 @@
         <v>900</v>
       </c>
       <c r="B901" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="902">
@@ -7645,7 +7645,7 @@
         <v>901</v>
       </c>
       <c r="B902" t="n">
-        <v>0</v>
+        <v>0.2996875</v>
       </c>
     </row>
     <row r="903">
@@ -7661,7 +7661,7 @@
         <v>903</v>
       </c>
       <c r="B904" t="n">
-        <v>0</v>
+        <v>0.769375</v>
       </c>
     </row>
     <row r="905">
@@ -7669,7 +7669,7 @@
         <v>904</v>
       </c>
       <c r="B905" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="906">
@@ -7685,7 +7685,7 @@
         <v>906</v>
       </c>
       <c r="B907" t="n">
-        <v>0</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="908">
@@ -7693,7 +7693,7 @@
         <v>907</v>
       </c>
       <c r="B908" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="909">
@@ -7701,7 +7701,7 @@
         <v>908</v>
       </c>
       <c r="B909" t="n">
-        <v>0</v>
+        <v>0.9746875</v>
       </c>
     </row>
     <row r="910">
@@ -7717,7 +7717,7 @@
         <v>910</v>
       </c>
       <c r="B911" t="n">
-        <v>0</v>
+        <v>0.7285937499999999</v>
       </c>
     </row>
     <row r="912">
@@ -7725,7 +7725,7 @@
         <v>911</v>
       </c>
       <c r="B912" t="n">
-        <v>0</v>
+        <v>0.9662500000000001</v>
       </c>
     </row>
     <row r="913">
@@ -7741,7 +7741,7 @@
         <v>913</v>
       </c>
       <c r="B914" t="n">
-        <v>0.5753125</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="915">
@@ -7749,7 +7749,7 @@
         <v>914</v>
       </c>
       <c r="B915" t="n">
-        <v>0.4093749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="916">
@@ -7757,7 +7757,7 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>0</v>
+        <v>0.9184375</v>
       </c>
     </row>
     <row r="917">
@@ -7773,7 +7773,7 @@
         <v>917</v>
       </c>
       <c r="B918" t="n">
-        <v>0</v>
+        <v>0.9578125</v>
       </c>
     </row>
     <row r="919">
@@ -7781,7 +7781,7 @@
         <v>918</v>
       </c>
       <c r="B919" t="n">
-        <v>0</v>
+        <v>0.8228124999999999</v>
       </c>
     </row>
     <row r="920">
@@ -7789,7 +7789,7 @@
         <v>919</v>
       </c>
       <c r="B920" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="921">
@@ -7797,7 +7797,7 @@
         <v>920</v>
       </c>
       <c r="B921" t="n">
-        <v>0</v>
+        <v>0.90578125</v>
       </c>
     </row>
     <row r="922">
@@ -7805,7 +7805,7 @@
         <v>921</v>
       </c>
       <c r="B922" t="n">
-        <v>0.55984375</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="923">
@@ -7813,7 +7813,7 @@
         <v>922</v>
       </c>
       <c r="B923" t="n">
-        <v>0</v>
+        <v>0.69484375</v>
       </c>
     </row>
     <row r="924">
@@ -7821,7 +7821,7 @@
         <v>923</v>
       </c>
       <c r="B924" t="n">
-        <v>0</v>
+        <v>0.95921875</v>
       </c>
     </row>
     <row r="925">
@@ -7829,7 +7829,7 @@
         <v>924</v>
       </c>
       <c r="B925" t="n">
-        <v>0.41359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="926">
@@ -7845,7 +7845,7 @@
         <v>926</v>
       </c>
       <c r="B927" t="n">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="928">
@@ -7853,7 +7853,7 @@
         <v>927</v>
       </c>
       <c r="B928" t="n">
-        <v>0</v>
+        <v>0.97609375</v>
       </c>
     </row>
     <row r="929">
@@ -7861,7 +7861,7 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>0</v>
+        <v>0.93953125</v>
       </c>
     </row>
     <row r="930">
@@ -7877,7 +7877,7 @@
         <v>930</v>
       </c>
       <c r="B931" t="n">
-        <v>0.92265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="932">
@@ -7885,7 +7885,7 @@
         <v>931</v>
       </c>
       <c r="B932" t="n">
-        <v>0</v>
+        <v>0.43046875</v>
       </c>
     </row>
     <row r="933">
@@ -7893,7 +7893,7 @@
         <v>932</v>
       </c>
       <c r="B933" t="n">
-        <v>0.6231249999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="934">
@@ -7901,7 +7901,7 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>0</v>
+        <v>0.8734375</v>
       </c>
     </row>
     <row r="935">
@@ -7909,7 +7909,7 @@
         <v>934</v>
       </c>
       <c r="B935" t="n">
-        <v>0</v>
+        <v>0.6526562499999999</v>
       </c>
     </row>
     <row r="936">
@@ -7925,7 +7925,7 @@
         <v>936</v>
       </c>
       <c r="B937" t="n">
-        <v>0.6203125</v>
+        <v>0.96484375</v>
       </c>
     </row>
     <row r="938">
@@ -7941,7 +7941,7 @@
         <v>938</v>
       </c>
       <c r="B939" t="n">
-        <v>0.325</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="940">
@@ -7949,7 +7949,7 @@
         <v>939</v>
       </c>
       <c r="B940" t="n">
-        <v>0.49515625</v>
+        <v>0.8987499999999999</v>
       </c>
     </row>
     <row r="941">
@@ -7957,7 +7957,7 @@
         <v>940</v>
       </c>
       <c r="B941" t="n">
-        <v>0</v>
+        <v>0.7904687500000001</v>
       </c>
     </row>
     <row r="942">
@@ -7965,7 +7965,7 @@
         <v>941</v>
       </c>
       <c r="B942" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="943">
@@ -7973,7 +7973,7 @@
         <v>942</v>
       </c>
       <c r="B943" t="n">
-        <v>0.6203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944">
@@ -7981,7 +7981,7 @@
         <v>943</v>
       </c>
       <c r="B944" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="945">
@@ -7997,7 +7997,7 @@
         <v>945</v>
       </c>
       <c r="B946" t="n">
-        <v>0.56546875</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="947">
@@ -8005,7 +8005,7 @@
         <v>946</v>
       </c>
       <c r="B947" t="n">
-        <v>0</v>
+        <v>0.72578125</v>
       </c>
     </row>
     <row r="948">
@@ -8013,7 +8013,7 @@
         <v>947</v>
       </c>
       <c r="B948" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="949">
@@ -8021,7 +8021,7 @@
         <v>948</v>
       </c>
       <c r="B949" t="n">
-        <v>0.3165625</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="950">
@@ -8045,7 +8045,7 @@
         <v>951</v>
       </c>
       <c r="B952" t="n">
-        <v>0.7553125000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="953">
@@ -8053,7 +8053,7 @@
         <v>952</v>
       </c>
       <c r="B953" t="n">
-        <v>0</v>
+        <v>0.4389062500000001</v>
       </c>
     </row>
     <row r="954">
@@ -8069,7 +8069,7 @@
         <v>954</v>
       </c>
       <c r="B955" t="n">
-        <v>0.3742187499999999</v>
+        <v>0.85234375</v>
       </c>
     </row>
     <row r="956">
@@ -8077,7 +8077,7 @@
         <v>955</v>
       </c>
       <c r="B956" t="n">
-        <v>0</v>
+        <v>0.97046875</v>
       </c>
     </row>
     <row r="957">
@@ -8085,7 +8085,7 @@
         <v>956</v>
       </c>
       <c r="B957" t="n">
-        <v>0</v>
+        <v>0.47265625</v>
       </c>
     </row>
     <row r="958">
@@ -8093,7 +8093,7 @@
         <v>957</v>
       </c>
       <c r="B958" t="n">
-        <v>0.94375</v>
+        <v>0.92265625</v>
       </c>
     </row>
     <row r="959">
@@ -8101,7 +8101,7 @@
         <v>958</v>
       </c>
       <c r="B959" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="960">
@@ -8109,7 +8109,7 @@
         <v>959</v>
       </c>
       <c r="B960" t="n">
-        <v>0</v>
+        <v>0.8284374999999999</v>
       </c>
     </row>
     <row r="961">
@@ -8117,7 +8117,7 @@
         <v>960</v>
       </c>
       <c r="B961" t="n">
-        <v>0</v>
+        <v>0.915625</v>
       </c>
     </row>
     <row r="962">
@@ -8133,7 +8133,7 @@
         <v>962</v>
       </c>
       <c r="B963" t="n">
-        <v>0</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="964">
@@ -8141,7 +8141,7 @@
         <v>963</v>
       </c>
       <c r="B964" t="n">
-        <v>0</v>
+        <v>0.92125</v>
       </c>
     </row>
     <row r="965">
@@ -8149,7 +8149,7 @@
         <v>964</v>
       </c>
       <c r="B965" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
     <row r="966">
@@ -8165,7 +8165,7 @@
         <v>966</v>
       </c>
       <c r="B967" t="n">
-        <v>0.53171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="968">
@@ -8181,7 +8181,7 @@
         <v>968</v>
       </c>
       <c r="B969" t="n">
-        <v>0.465625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="970">
@@ -8189,7 +8189,7 @@
         <v>969</v>
       </c>
       <c r="B970" t="n">
-        <v>0</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="971">
@@ -8197,7 +8197,7 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>0.533125</v>
+        <v>0.90296875</v>
       </c>
     </row>
     <row r="972">
@@ -8205,7 +8205,7 @@
         <v>971</v>
       </c>
       <c r="B972" t="n">
-        <v>0</v>
+        <v>0.94515625</v>
       </c>
     </row>
     <row r="973">
@@ -8213,7 +8213,7 @@
         <v>972</v>
       </c>
       <c r="B973" t="n">
-        <v>0.91984375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="974">
@@ -8221,7 +8221,7 @@
         <v>973</v>
       </c>
       <c r="B974" t="n">
-        <v>0</v>
+        <v>0.960625</v>
       </c>
     </row>
     <row r="975">
@@ -8229,7 +8229,7 @@
         <v>974</v>
       </c>
       <c r="B975" t="n">
-        <v>0</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="976">
@@ -8237,7 +8237,7 @@
         <v>975</v>
       </c>
       <c r="B976" t="n">
-        <v>0</v>
+        <v>0.98171875</v>
       </c>
     </row>
     <row r="977">
@@ -8245,7 +8245,7 @@
         <v>976</v>
       </c>
       <c r="B977" t="n">
-        <v>0</v>
+        <v>0.5401562499999999</v>
       </c>
     </row>
     <row r="978">
@@ -8253,7 +8253,7 @@
         <v>977</v>
       </c>
       <c r="B978" t="n">
-        <v>0.791875</v>
+        <v>0.8115625</v>
       </c>
     </row>
     <row r="979">
@@ -8285,7 +8285,7 @@
         <v>981</v>
       </c>
       <c r="B982" t="n">
-        <v>0</v>
+        <v>0.9690625</v>
       </c>
     </row>
     <row r="983">
@@ -8293,7 +8293,7 @@
         <v>982</v>
       </c>
       <c r="B983" t="n">
-        <v>0.61328125</v>
+        <v>0.8115625</v>
       </c>
     </row>
     <row r="984">
@@ -8317,7 +8317,7 @@
         <v>985</v>
       </c>
       <c r="B986" t="n">
-        <v>0.4093749999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="987">
@@ -8333,7 +8333,7 @@
         <v>987</v>
       </c>
       <c r="B988" t="n">
-        <v>0.533125</v>
+        <v>0.9353125</v>
       </c>
     </row>
     <row r="989">
@@ -8341,7 +8341,7 @@
         <v>988</v>
       </c>
       <c r="B989" t="n">
-        <v>0.94234375</v>
+        <v>0.7932812499999999</v>
       </c>
     </row>
     <row r="990">
@@ -8365,7 +8365,7 @@
         <v>991</v>
       </c>
       <c r="B992" t="n">
-        <v>0</v>
+        <v>0.97890625</v>
       </c>
     </row>
     <row r="993">
@@ -8373,7 +8373,7 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>0.6315625</v>
+        <v>0.4557812499999999</v>
       </c>
     </row>
     <row r="994">
@@ -8381,7 +8381,7 @@
         <v>993</v>
       </c>
       <c r="B994" t="n">
-        <v>0</v>
+        <v>0.97328125</v>
       </c>
     </row>
     <row r="995">
@@ -8389,7 +8389,7 @@
         <v>994</v>
       </c>
       <c r="B995" t="n">
-        <v>0</v>
+        <v>0.42625</v>
       </c>
     </row>
     <row r="996">
@@ -8397,7 +8397,7 @@
         <v>995</v>
       </c>
       <c r="B996" t="n">
-        <v>0.8579687499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="997">
@@ -8405,7 +8405,7 @@
         <v>996</v>
       </c>
       <c r="B997" t="n">
-        <v>0.74828125</v>
+        <v>0.95640625</v>
       </c>
     </row>
     <row r="998">
@@ -8429,7 +8429,7 @@
         <v>999</v>
       </c>
       <c r="B1000" t="n">
-        <v>0</v>
+        <v>0.3981250000000001</v>
       </c>
     </row>
     <row r="1001">
@@ -8437,7 +8437,7 @@
         <v>1000</v>
       </c>
       <c r="B1001" t="n">
-        <v>0</v>
+        <v>0.9803125</v>
       </c>
     </row>
   </sheetData>
